--- a/internship_application_form_templates/043_summer_intern_application_2013--internship_application_form_templates.xlsx
+++ b/internship_application_form_templates/043_summer_intern_application_2013--internship_application_form_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -740,7 +740,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_details_0</t>
+          <t>contact_details_0_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_details_0</t>
+          <t>contact_details_0_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_details_0</t>
+          <t>contact_details_0_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Educational Info 0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>educational_info_0</t>
+          <t>educational_info_0_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>educational_info_0</t>
+          <t>educational_info_0_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>educational_info_0</t>
+          <t>educational_info_0_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>major</t>
+          <t>Major 0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>church_affiliation</t>
+          <t>Church Affiliation 0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>experiences</t>
+          <t>Experiences 0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>employment_details</t>
+          <t>Employment Details 0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>references</t>
+          <t>References 0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
